--- a/Hoàng/2025/T6/CÔNG TY CP THƯƠNG MẠI CỔNG VÀNG/BG THIỆN NHÂN - CÔNG TY CỔ PHẦN THƯƠNG MẠI CỔNG VÀNG ĐIỀU CHỈNH.xlsx
+++ b/Hoàng/2025/T6/CÔNG TY CP THƯƠNG MẠI CỔNG VÀNG/BG THIỆN NHÂN - CÔNG TY CỔ PHẦN THƯƠNG MẠI CỔNG VÀNG ĐIỀU CHỈNH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CÔNG TY CP THƯƠNG MẠI CỔNG VÀNG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDB8D3C-EE49-46F5-A9B5-10FB1A28400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C192A78-29BF-4B57-A331-E22DCB603A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,6 +1087,69 @@
     <xf numFmtId="3" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1156,15 +1219,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1174,27 +1228,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1205,39 +1238,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1636,53 +1636,53 @@
       <c r="A1" s="20"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
     </row>
     <row r="5" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="6" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
@@ -1695,16 +1695,16 @@
       <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="97" t="s">
+      <c r="A7" s="118" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="97"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -1728,31 +1728,31 @@
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="101"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="122"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -1760,14 +1760,14 @@
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="125"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
@@ -1785,41 +1785,41 @@
       <c r="H12" s="30"/>
     </row>
     <row r="13" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="125" t="s">
+      <c r="A13" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="125" t="s">
+      <c r="C13" s="139"/>
+      <c r="D13" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="140" t="s">
+      <c r="E13" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="138" t="s">
+      <c r="F13" s="94" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="139"/>
-      <c r="H13" s="133" t="s">
+      <c r="G13" s="95"/>
+      <c r="H13" s="103" t="s">
         <v>0</v>
       </c>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="126"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="141"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="99"/>
       <c r="F14" s="61" t="s">
         <v>108</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="134"/>
+      <c r="H14" s="104"/>
       <c r="I14" s="10"/>
     </row>
     <row r="15" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1964,7 +1964,7 @@
       <c r="A21" s="33">
         <v>6</v>
       </c>
-      <c r="B21" s="120" t="s">
+      <c r="B21" s="102" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="36" t="s">
@@ -1973,16 +1973,16 @@
       <c r="D21" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="121">
+      <c r="E21" s="96">
         <v>60000</v>
       </c>
-      <c r="F21" s="121" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="121" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="123" t="s">
+      <c r="F21" s="96" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="96" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="105" t="s">
         <v>98</v>
       </c>
       <c r="I21" s="12"/>
@@ -1991,17 +1991,17 @@
       <c r="A22" s="33">
         <v>7</v>
       </c>
-      <c r="B22" s="120"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="36" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="122"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="124"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="106"/>
       <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:9" ht="66" x14ac:dyDescent="0.25">
@@ -2072,7 +2072,7 @@
       <c r="G25" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="135" t="s">
+      <c r="H25" s="107" t="s">
         <v>97</v>
       </c>
       <c r="I25" s="12"/>
@@ -2097,7 +2097,7 @@
       <c r="G26" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="H26" s="136"/>
+      <c r="H26" s="108"/>
       <c r="I26" s="12"/>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2122,7 +2122,7 @@
       <c r="G27" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="136"/>
+      <c r="H27" s="108"/>
       <c r="I27" s="12"/>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2145,7 +2145,7 @@
       <c r="G28" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="H28" s="137"/>
+      <c r="H28" s="109"/>
       <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:9" ht="33" x14ac:dyDescent="0.25">
@@ -2198,7 +2198,7 @@
       <c r="A31" s="33">
         <v>16</v>
       </c>
-      <c r="B31" s="120" t="s">
+      <c r="B31" s="102" t="s">
         <v>103</v>
       </c>
       <c r="C31" s="31" t="s">
@@ -2207,16 +2207,16 @@
       <c r="D31" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="114">
+      <c r="E31" s="91">
         <v>123000</v>
       </c>
-      <c r="F31" s="114" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="114" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="123" t="s">
+      <c r="F31" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="105" t="s">
         <v>102</v>
       </c>
       <c r="I31" s="12"/>
@@ -2225,24 +2225,24 @@
       <c r="A32" s="33">
         <v>17</v>
       </c>
-      <c r="B32" s="120"/>
+      <c r="B32" s="102"/>
       <c r="C32" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D32" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="116"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="116"/>
-      <c r="H32" s="124"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="106"/>
       <c r="I32" s="12"/>
     </row>
     <row r="33" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>18</v>
       </c>
-      <c r="B33" s="120"/>
+      <c r="B33" s="102"/>
       <c r="C33" s="31" t="s">
         <v>70</v>
       </c>
@@ -2344,93 +2344,93 @@
       <c r="I37" s="76"/>
     </row>
     <row r="38" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="105">
+      <c r="A38" s="126">
         <v>22</v>
       </c>
-      <c r="B38" s="108" t="s">
+      <c r="B38" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="111" t="s">
+      <c r="C38" s="132" t="s">
         <v>91</v>
       </c>
       <c r="D38" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E38" s="114">
+      <c r="E38" s="91">
         <v>200000</v>
       </c>
-      <c r="F38" s="114" t="s">
-        <v>111</v>
-      </c>
-      <c r="G38" s="114" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="117"/>
+      <c r="F38" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" s="135"/>
       <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="106"/>
-      <c r="B39" s="109"/>
-      <c r="C39" s="112"/>
+      <c r="A39" s="127"/>
+      <c r="B39" s="130"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="115"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="115"/>
-      <c r="H39" s="118"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="136"/>
       <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A40" s="106"/>
-      <c r="B40" s="109"/>
-      <c r="C40" s="112"/>
+      <c r="A40" s="127"/>
+      <c r="B40" s="130"/>
+      <c r="C40" s="133"/>
       <c r="D40" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="115"/>
-      <c r="F40" s="115"/>
-      <c r="G40" s="115"/>
-      <c r="H40" s="118"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="136"/>
       <c r="I40" s="11"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="106"/>
-      <c r="B41" s="109"/>
-      <c r="C41" s="112"/>
+      <c r="A41" s="127"/>
+      <c r="B41" s="130"/>
+      <c r="C41" s="133"/>
       <c r="D41" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="115"/>
-      <c r="F41" s="115"/>
-      <c r="G41" s="115"/>
-      <c r="H41" s="118"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="136"/>
       <c r="I41" s="12"/>
     </row>
     <row r="42" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="106"/>
-      <c r="B42" s="109"/>
-      <c r="C42" s="112"/>
+      <c r="A42" s="127"/>
+      <c r="B42" s="130"/>
+      <c r="C42" s="133"/>
       <c r="D42" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="115"/>
-      <c r="H42" s="118"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="136"/>
       <c r="I42" s="12"/>
     </row>
     <row r="43" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="107"/>
-      <c r="B43" s="110"/>
-      <c r="C43" s="113"/>
+      <c r="A43" s="128"/>
+      <c r="B43" s="131"/>
+      <c r="C43" s="134"/>
       <c r="D43" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="116"/>
-      <c r="F43" s="116"/>
-      <c r="G43" s="116"/>
-      <c r="H43" s="119"/>
+      <c r="E43" s="93"/>
+      <c r="F43" s="93"/>
+      <c r="G43" s="93"/>
+      <c r="H43" s="137"/>
       <c r="I43" s="12"/>
     </row>
     <row r="44" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -2658,12 +2658,12 @@
       <c r="I53" s="13"/>
     </row>
     <row r="54" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="92" t="s">
+      <c r="A54" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="93"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="94"/>
+      <c r="B54" s="114"/>
+      <c r="C54" s="114"/>
+      <c r="D54" s="115"/>
       <c r="E54" s="61">
         <f>SUM(E16:E53)</f>
         <v>3492000</v>
@@ -2734,12 +2734,12 @@
       <c r="H59" s="47"/>
     </row>
     <row r="60" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="91" t="s">
+      <c r="A60" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="91"/>
-      <c r="C60" s="91"/>
-      <c r="D60" s="91"/>
+      <c r="B60" s="112"/>
+      <c r="C60" s="112"/>
+      <c r="D60" s="112"/>
       <c r="E60" s="24"/>
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
@@ -2747,63 +2747,63 @@
     </row>
     <row r="61" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="49"/>
-      <c r="B61" s="131" t="s">
+      <c r="B61" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="131"/>
-      <c r="D61" s="131"/>
-      <c r="E61" s="131"/>
-      <c r="F61" s="131"/>
-      <c r="G61" s="131"/>
-      <c r="H61" s="131"/>
+      <c r="C61" s="110"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="110"/>
+      <c r="G61" s="110"/>
+      <c r="H61" s="110"/>
     </row>
     <row r="62" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="49"/>
-      <c r="B62" s="131" t="s">
+      <c r="B62" s="110" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="131"/>
-      <c r="D62" s="131"/>
-      <c r="E62" s="131"/>
-      <c r="F62" s="131"/>
-      <c r="G62" s="131"/>
-      <c r="H62" s="131"/>
+      <c r="C62" s="110"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110"/>
     </row>
     <row r="63" spans="1:9" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="50"/>
-      <c r="B63" s="131" t="s">
+      <c r="B63" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="C63" s="131"/>
-      <c r="D63" s="131"/>
-      <c r="E63" s="131"/>
-      <c r="F63" s="131"/>
-      <c r="G63" s="131"/>
-      <c r="H63" s="131"/>
+      <c r="C63" s="110"/>
+      <c r="D63" s="110"/>
+      <c r="E63" s="110"/>
+      <c r="F63" s="110"/>
+      <c r="G63" s="110"/>
+      <c r="H63" s="110"/>
     </row>
     <row r="64" spans="1:9" s="15" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="51"/>
-      <c r="B64" s="132" t="s">
+      <c r="B64" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="132"/>
-      <c r="D64" s="132"/>
-      <c r="E64" s="132"/>
-      <c r="F64" s="132"/>
-      <c r="G64" s="132"/>
-      <c r="H64" s="132"/>
+      <c r="C64" s="111"/>
+      <c r="D64" s="111"/>
+      <c r="E64" s="111"/>
+      <c r="F64" s="111"/>
+      <c r="G64" s="111"/>
+      <c r="H64" s="111"/>
     </row>
     <row r="65" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="48"/>
-      <c r="B65" s="131" t="s">
+      <c r="B65" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="C65" s="131"/>
-      <c r="D65" s="131"/>
-      <c r="E65" s="131"/>
-      <c r="F65" s="131"/>
-      <c r="G65" s="131"/>
-      <c r="H65" s="131"/>
+      <c r="C65" s="110"/>
+      <c r="D65" s="110"/>
+      <c r="E65" s="110"/>
+      <c r="F65" s="110"/>
+      <c r="G65" s="110"/>
+      <c r="H65" s="110"/>
     </row>
     <row r="66" spans="1:8" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="48"/>
@@ -2879,25 +2879,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="F38:F43"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B63:H63"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B65:H65"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="D1:H5"/>
@@ -2914,6 +2895,25 @@
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:C14"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H25:H28"/>
+    <mergeCell ref="F38:F43"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:C36 C38:C1048576 C1:C12">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
